--- a/ACCY122/Session/S06/ACCY122 In Session L6 v1.0.xlsx
+++ b/ACCY122/Session/S06/ACCY122 In Session L6 v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Session\S06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AD6CAE36-8DB8-4D76-A079-3EB780A4C7D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F0FEE3-9CA9-4A04-BACF-F5EDEA1A5D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{BB81D00E-B7BD-4C7E-833A-F8ECA5DA9AD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{BB81D00E-B7BD-4C7E-833A-F8ECA5DA9AD9}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="7" r:id="rId1"/>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="109">
   <si>
     <t>Input</t>
   </si>
@@ -438,6 +438,42 @@
   </si>
   <si>
     <t>To reset drawing to 0</t>
+  </si>
+  <si>
+    <t>1. Cash receipts journal</t>
+  </si>
+  <si>
+    <t>2. Purchases journal</t>
+  </si>
+  <si>
+    <t>3. Cash payments journal</t>
+  </si>
+  <si>
+    <t>4. Cash receipts journal</t>
+  </si>
+  <si>
+    <t>5. Sales journal</t>
+  </si>
+  <si>
+    <t>6. Cash receipts journal</t>
+  </si>
+  <si>
+    <t>7. General journal</t>
+  </si>
+  <si>
+    <t>8. General journal</t>
+  </si>
+  <si>
+    <t>9. Cash payments journal</t>
+  </si>
+  <si>
+    <t>10. Cash payments journal</t>
+  </si>
+  <si>
+    <t>11. Cash payments journal</t>
+  </si>
+  <si>
+    <t>12. General journal</t>
   </si>
 </sst>
 </file>
@@ -630,19 +666,19 @@
     <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2217,7 +2253,7 @@
       </c>
     </row>
     <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="16" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2239,11 +2275,11 @@
       </c>
     </row>
     <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="17" t="s">
+      <c r="C4" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="17"/>
-      <c r="E4" s="17" t="s">
+      <c r="D4" s="16"/>
+      <c r="E4" s="16" t="s">
         <v>3</v>
       </c>
       <c r="F4" t="s">
@@ -2257,9 +2293,9 @@
       </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C5" s="17"/>
-      <c r="D5" s="17"/>
-      <c r="E5" s="18" t="s">
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="17" t="s">
         <v>12</v>
       </c>
       <c r="M5" s="5"/>
@@ -2274,14 +2310,14 @@
       <c r="C6" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="D6" s="17"/>
-      <c r="E6" s="17" t="s">
+      <c r="D6" s="16"/>
+      <c r="E6" s="16" t="s">
         <v>41</v>
       </c>
       <c r="F6" t="s">
         <v>65</v>
       </c>
-      <c r="H6" s="17" t="s">
+      <c r="H6" s="16" t="s">
         <v>71</v>
       </c>
       <c r="K6">
@@ -2300,8 +2336,8 @@
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C7" s="22"/>
-      <c r="D7" s="17"/>
-      <c r="E7" s="18" t="s">
+      <c r="D7" s="16"/>
+      <c r="E7" s="17" t="s">
         <v>12</v>
       </c>
       <c r="M7" s="8" t="s">
@@ -2313,8 +2349,8 @@
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C8" s="22"/>
-      <c r="D8" s="17"/>
-      <c r="E8" s="17" t="s">
+      <c r="D8" s="16"/>
+      <c r="E8" s="16" t="s">
         <v>75</v>
       </c>
       <c r="F8" t="s">
@@ -2327,8 +2363,8 @@
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C9" s="22"/>
-      <c r="D9" s="17"/>
-      <c r="E9" s="18" t="s">
+      <c r="D9" s="16"/>
+      <c r="E9" s="17" t="s">
         <v>12</v>
       </c>
       <c r="M9" s="8"/>
@@ -2336,8 +2372,8 @@
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
       <c r="C10" s="22"/>
-      <c r="D10" s="17"/>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="16"/>
+      <c r="E10" s="16" t="s">
         <v>77</v>
       </c>
       <c r="F10" t="s">
@@ -2364,16 +2400,16 @@
       <c r="O10" s="9"/>
     </row>
     <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="17"/>
-      <c r="D11" s="17"/>
-      <c r="E11" s="17"/>
-      <c r="F11" s="19" t="s">
+      <c r="C11" s="16"/>
+      <c r="D11" s="16"/>
+      <c r="E11" s="16"/>
+      <c r="F11" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="20" t="s">
+      <c r="G11" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H11" s="21" t="s">
+      <c r="H11" s="20" t="s">
         <v>83</v>
       </c>
       <c r="M11" s="8" t="s">
@@ -2384,9 +2420,9 @@
       </c>
     </row>
     <row r="12" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="17"/>
-      <c r="D12" s="17"/>
-      <c r="E12" s="18" t="s">
+      <c r="C12" s="16"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="17" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="1" t="s">
@@ -2401,11 +2437,11 @@
       <c r="O12" s="9"/>
     </row>
     <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C13" s="17" t="s">
+      <c r="C13" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="D13" s="17"/>
-      <c r="E13" s="17" t="s">
+      <c r="D13" s="16"/>
+      <c r="E13" s="16" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
@@ -2548,7 +2584,7 @@
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="21" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2574,7 +2610,7 @@
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="23"/>
+      <c r="B6" s="21"/>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
@@ -2595,11 +2631,11 @@
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="23"/>
+      <c r="B7" s="21"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="23"/>
+      <c r="B8" s="21"/>
       <c r="C8" s="2" t="s">
         <v>5</v>
       </c>
@@ -2617,7 +2653,7 @@
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="23"/>
+      <c r="B9" s="21"/>
       <c r="C9" s="3" t="s">
         <v>12</v>
       </c>
@@ -2632,7 +2668,7 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="23"/>
+      <c r="B10" s="21"/>
       <c r="C10" s="3"/>
       <c r="E10" t="s">
         <v>46</v>
@@ -2642,7 +2678,7 @@
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="23"/>
+      <c r="B11" s="21"/>
       <c r="C11" s="2" t="s">
         <v>6</v>
       </c>
@@ -2968,9 +3004,73 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CA200DE-4AC7-48D2-AFD1-785C8C2141F6}">
-  <dimension ref="A1"/>
+  <dimension ref="B26:D37"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <sheetData/>
+  <sheetData>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="16"/>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B33" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C34" s="16"/>
+      <c r="D34" s="16"/>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B35" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B37" t="s">
+        <v>108</v>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
 </worksheet>
@@ -3017,10 +3117,10 @@
       </c>
     </row>
     <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L7">
+      <c r="L7" s="16">
         <v>4</v>
       </c>
-      <c r="M7" t="s">
+      <c r="M7" s="16" t="s">
         <v>49</v>
       </c>
     </row>
@@ -3041,18 +3141,18 @@
       </c>
     </row>
     <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L10" s="16" t="s">
+      <c r="L10" s="23" t="s">
         <v>56</v>
       </c>
-      <c r="M10" t="s">
+      <c r="M10" s="16" t="s">
         <v>50</v>
       </c>
     </row>
     <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L11" s="16" t="s">
+      <c r="L11" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="M11" t="s">
+      <c r="M11" s="16" t="s">
         <v>47</v>
       </c>
     </row>
@@ -3089,10 +3189,10 @@
       </c>
     </row>
     <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L16">
+      <c r="L16" s="16">
         <v>16</v>
       </c>
-      <c r="M16" t="s">
+      <c r="M16" s="16" t="s">
         <v>50</v>
       </c>
     </row>

--- a/ACCY122/Session/S06/ACCY122 In Session L6 v1.0.xlsx
+++ b/ACCY122/Session/S06/ACCY122 In Session L6 v1.0.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\josep\Desktop\SIM-UOW-Mods\ACCY122\Session\S06\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02F0FEE3-9CA9-4A04-BACF-F5EDEA1A5D52}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65D161F9-46A4-4AE9-8BC8-20BFE8675F1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{BB81D00E-B7BD-4C7E-833A-F8ECA5DA9AD9}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="5" xr2:uid="{BB81D00E-B7BD-4C7E-833A-F8ECA5DA9AD9}"/>
   </bookViews>
   <sheets>
     <sheet name="System" sheetId="7" r:id="rId1"/>
@@ -109,7 +109,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="108">
   <si>
     <t>Input</t>
   </si>
@@ -265,9 +265,6 @@
   </si>
   <si>
     <t>GJ</t>
-  </si>
-  <si>
-    <t>Date</t>
   </si>
   <si>
     <t>TRANSACTIONS</t>
@@ -647,7 +644,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
@@ -663,7 +660,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1"/>
-    <xf numFmtId="17" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
@@ -671,14 +667,14 @@
     <xf numFmtId="0" fontId="0" fillId="5" borderId="9" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1523,15 +1519,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>196360</xdr:colOff>
+      <xdr:colOff>328881</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>162584</xdr:rowOff>
+      <xdr:rowOff>154301</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>11</xdr:col>
-      <xdr:colOff>180260</xdr:colOff>
+      <xdr:colOff>312781</xdr:colOff>
       <xdr:row>25</xdr:row>
-      <xdr:rowOff>165271</xdr:rowOff>
+      <xdr:rowOff>156988</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1561,8 +1557,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="196360" y="530700"/>
-          <a:ext cx="6971968" cy="4236020"/>
+          <a:off x="328881" y="535301"/>
+          <a:ext cx="6949574" cy="4384187"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2249,85 +2245,85 @@
   <sheetData>
     <row r="1" spans="2:15" x14ac:dyDescent="0.25">
       <c r="G1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="B2" s="15" t="s">
         <v>58</v>
-      </c>
-    </row>
-    <row r="2" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="B2" s="16" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F3" t="s">
+        <v>59</v>
+      </c>
+      <c r="G3" t="s">
         <v>60</v>
       </c>
-      <c r="G3" t="s">
+      <c r="H3" t="s">
+        <v>58</v>
+      </c>
+      <c r="L3" t="s">
         <v>61</v>
       </c>
-      <c r="H3" t="s">
-        <v>59</v>
-      </c>
-      <c r="L3" t="s">
+      <c r="M3" t="s">
         <v>62</v>
       </c>
-      <c r="M3" t="s">
+    </row>
+    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="15" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="4" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C4" s="16" t="s">
+      <c r="D4" s="15"/>
+      <c r="E4" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="F4" t="s">
         <v>64</v>
       </c>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16" t="s">
-        <v>3</v>
-      </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>65</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>66</v>
       </c>
-      <c r="H4" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="5" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="17" t="s">
+      <c r="C5" s="15"/>
+      <c r="D5" s="15"/>
+      <c r="E5" s="16" t="s">
         <v>12</v>
       </c>
       <c r="M5" s="5"/>
       <c r="N5" s="6" t="s">
+        <v>67</v>
+      </c>
+      <c r="O5" s="7" t="s">
         <v>68</v>
       </c>
-      <c r="O5" s="7" t="s">
+    </row>
+    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C6" s="21" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="6" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C6" s="22" t="s">
+      <c r="D6" s="15"/>
+      <c r="E6" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="F6" t="s">
+        <v>64</v>
+      </c>
+      <c r="H6" s="15" t="s">
         <v>70</v>
-      </c>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="F6" t="s">
-        <v>65</v>
-      </c>
-      <c r="H6" s="16" t="s">
-        <v>71</v>
       </c>
       <c r="K6">
         <v>1</v>
       </c>
       <c r="L6" t="s">
+        <v>71</v>
+      </c>
+      <c r="M6" s="8" t="s">
         <v>72</v>
-      </c>
-      <c r="M6" s="8" t="s">
-        <v>73</v>
       </c>
       <c r="N6" t="s">
         <v>30</v>
@@ -2335,64 +2331,64 @@
       <c r="O6" s="9"/>
     </row>
     <row r="7" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C7" s="22"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="17" t="s">
+      <c r="C7" s="21"/>
+      <c r="D7" s="15"/>
+      <c r="E7" s="16" t="s">
         <v>12</v>
       </c>
       <c r="M7" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="O7" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="8" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C8" s="22"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16" t="s">
+      <c r="C8" s="21"/>
+      <c r="D8" s="15"/>
+      <c r="E8" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F8" t="s">
+        <v>64</v>
+      </c>
+      <c r="M8" s="8" t="s">
         <v>75</v>
       </c>
-      <c r="F8" t="s">
-        <v>65</v>
-      </c>
-      <c r="M8" s="8" t="s">
-        <v>76</v>
-      </c>
       <c r="O8" s="9"/>
     </row>
     <row r="9" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C9" s="22"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="17" t="s">
+      <c r="C9" s="21"/>
+      <c r="D9" s="15"/>
+      <c r="E9" s="16" t="s">
         <v>12</v>
       </c>
       <c r="M9" s="8"/>
       <c r="O9" s="9"/>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C10" s="22"/>
-      <c r="D10" s="16"/>
-      <c r="E10" s="16" t="s">
+      <c r="C10" s="21"/>
+      <c r="D10" s="15"/>
+      <c r="E10" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="F10" t="s">
+        <v>64</v>
+      </c>
+      <c r="G10" t="s">
         <v>77</v>
       </c>
-      <c r="F10" t="s">
-        <v>65</v>
-      </c>
-      <c r="G10" t="s">
+      <c r="H10" t="s">
         <v>78</v>
-      </c>
-      <c r="H10" t="s">
-        <v>79</v>
       </c>
       <c r="K10">
         <v>2</v>
       </c>
       <c r="L10" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="M10" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N10" t="s">
         <v>30</v>
@@ -2400,71 +2396,71 @@
       <c r="O10" s="9"/>
     </row>
     <row r="11" spans="2:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C11" s="16"/>
-      <c r="D11" s="16"/>
-      <c r="E11" s="16"/>
-      <c r="F11" s="18" t="s">
+      <c r="C11" s="15"/>
+      <c r="D11" s="15"/>
+      <c r="E11" s="15"/>
+      <c r="F11" s="17" t="s">
+        <v>80</v>
+      </c>
+      <c r="G11" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G11" s="19" t="s">
+      <c r="H11" s="19" t="s">
         <v>82</v>
       </c>
-      <c r="H11" s="20" t="s">
+      <c r="M11" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="M11" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="O11" s="9" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="12" spans="2:15" ht="15.75" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="17" t="s">
+      <c r="C12" s="15"/>
+      <c r="D12" s="15"/>
+      <c r="E12" s="16" t="s">
         <v>12</v>
       </c>
       <c r="G12" s="1" t="s">
         <v>12</v>
       </c>
       <c r="H12" t="s">
+        <v>84</v>
+      </c>
+      <c r="M12" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="M12" s="8" t="s">
+      <c r="O12" s="9"/>
+    </row>
+    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
+      <c r="C13" s="15" t="s">
         <v>86</v>
       </c>
-      <c r="O12" s="9"/>
-    </row>
-    <row r="13" spans="2:15" x14ac:dyDescent="0.25">
-      <c r="C13" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="D13" s="16"/>
-      <c r="E13" s="16" t="s">
+      <c r="D13" s="15"/>
+      <c r="E13" s="15" t="s">
         <v>7</v>
       </c>
       <c r="F13" t="s">
         <v>7</v>
       </c>
       <c r="H13" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="M13" s="8"/>
       <c r="O13" s="9"/>
     </row>
     <row r="14" spans="2:15" x14ac:dyDescent="0.25">
       <c r="F14" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="K14">
         <v>3</v>
       </c>
       <c r="L14" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="M14" s="8" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="N14" t="s">
         <v>30</v>
@@ -2473,7 +2469,7 @@
     </row>
     <row r="15" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M15" s="8" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="O15" s="9" t="s">
         <v>30</v>
@@ -2481,7 +2477,7 @@
     </row>
     <row r="16" spans="2:15" x14ac:dyDescent="0.25">
       <c r="M16" s="8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="O16" s="9"/>
     </row>
@@ -2494,10 +2490,10 @@
         <v>4</v>
       </c>
       <c r="L18" t="s">
+        <v>92</v>
+      </c>
+      <c r="M18" s="8" t="s">
         <v>93</v>
-      </c>
-      <c r="M18" s="8" t="s">
-        <v>94</v>
       </c>
       <c r="N18" t="s">
         <v>30</v>
@@ -2506,7 +2502,7 @@
     </row>
     <row r="19" spans="11:15" x14ac:dyDescent="0.25">
       <c r="M19" s="8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="O19" s="9" t="s">
         <v>30</v>
@@ -2514,7 +2510,7 @@
     </row>
     <row r="20" spans="11:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="M20" s="10" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="N20" s="11"/>
       <c r="O20" s="12"/>
@@ -2584,7 +2580,7 @@
       </c>
     </row>
     <row r="5" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B5" s="21" t="s">
+      <c r="B5" s="22" t="s">
         <v>1</v>
       </c>
       <c r="C5" s="2" t="s">
@@ -2610,15 +2606,15 @@
       </c>
     </row>
     <row r="6" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B6" s="21"/>
+      <c r="B6" s="22"/>
       <c r="C6" s="3" t="s">
         <v>12</v>
       </c>
       <c r="E6" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G6" t="s">
         <v>17</v>
@@ -2631,11 +2627,11 @@
       </c>
     </row>
     <row r="7" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B7" s="21"/>
+      <c r="B7" s="22"/>
       <c r="C7" s="3"/>
     </row>
     <row r="8" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B8" s="21"/>
+      <c r="B8" s="22"/>
       <c r="C8" s="2" t="s">
         <v>5</v>
       </c>
@@ -2653,7 +2649,7 @@
       </c>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B9" s="21"/>
+      <c r="B9" s="22"/>
       <c r="C9" s="3" t="s">
         <v>12</v>
       </c>
@@ -2668,7 +2664,7 @@
       </c>
     </row>
     <row r="10" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B10" s="21"/>
+      <c r="B10" s="22"/>
       <c r="C10" s="3"/>
       <c r="E10" t="s">
         <v>46</v>
@@ -2678,7 +2674,7 @@
       </c>
     </row>
     <row r="11" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="B11" s="21"/>
+      <c r="B11" s="22"/>
       <c r="C11" s="2" t="s">
         <v>6</v>
       </c>
@@ -2756,8 +2752,8 @@
   <sheetData>
     <row r="1" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="2:10" x14ac:dyDescent="0.25">
-      <c r="B2" s="14" t="s">
-        <v>53</v>
+      <c r="B2" s="13" t="s">
+        <v>52</v>
       </c>
       <c r="C2" s="6"/>
       <c r="D2" s="7" t="s">
@@ -2821,7 +2817,7 @@
       </c>
     </row>
     <row r="9" spans="2:10" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B9" s="15" t="s">
+      <c r="B9" s="14" t="s">
         <v>41</v>
       </c>
     </row>
@@ -3009,65 +3005,65 @@
   <sheetData>
     <row r="26" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B26" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="27" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B27" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="28" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B28" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="29" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B29" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B30" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="31" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B31" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="15" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
-      <c r="B32" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C32" s="16"/>
+      <c r="C32" s="15"/>
     </row>
     <row r="33" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B33" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B34" s="15" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C34" s="16"/>
-      <c r="D34" s="16"/>
+      <c r="C34" s="15"/>
+      <c r="D34" s="15"/>
     </row>
     <row r="35" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B35" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="36" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B36" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="37" spans="2:4" x14ac:dyDescent="0.25">
       <c r="B37" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
   </sheetData>
@@ -3078,29 +3074,13 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C475F646-1768-4DC5-B0F6-68F5AAE46917}">
-  <dimension ref="B1:M24"/>
+  <dimension ref="L5:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B1" t="s">
-        <v>52</v>
-      </c>
-      <c r="C1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="B2" s="13">
-        <v>37043</v>
-      </c>
-      <c r="C2" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="5" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L5">
         <v>1</v>
       </c>
@@ -3108,7 +3088,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="6" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L6">
         <v>3</v>
       </c>
@@ -3116,15 +3096,15 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L7" s="16">
+    <row r="7" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L7" s="15">
         <v>4</v>
       </c>
-      <c r="M7" s="16" t="s">
+      <c r="M7" s="15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="8" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L8">
         <v>5</v>
       </c>
@@ -3132,7 +3112,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="9" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L9">
         <v>6</v>
       </c>
@@ -3140,23 +3120,23 @@
         <v>48</v>
       </c>
     </row>
-    <row r="10" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L10" s="23" t="s">
+    <row r="10" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L10" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="M10" s="15" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L11" s="20" t="s">
         <v>56</v>
       </c>
-      <c r="M10" s="16" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L11" s="23" t="s">
-        <v>57</v>
-      </c>
-      <c r="M11" s="16" t="s">
+      <c r="M11" s="15" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="12" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="12" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L12">
         <v>10</v>
       </c>
@@ -3164,7 +3144,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="13" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="13" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L13">
         <v>12</v>
       </c>
@@ -3172,7 +3152,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="14" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="14" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L14">
         <v>12</v>
       </c>
@@ -3180,7 +3160,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="15" spans="2:13" x14ac:dyDescent="0.25">
+    <row r="15" spans="12:13" x14ac:dyDescent="0.25">
       <c r="L15">
         <v>13</v>
       </c>
@@ -3188,11 +3168,11 @@
         <v>49</v>
       </c>
     </row>
-    <row r="16" spans="2:13" x14ac:dyDescent="0.25">
-      <c r="L16" s="16">
+    <row r="16" spans="12:13" x14ac:dyDescent="0.25">
+      <c r="L16" s="15">
         <v>16</v>
       </c>
-      <c r="M16" s="16" t="s">
+      <c r="M16" s="15" t="s">
         <v>50</v>
       </c>
     </row>
